--- a/data-raw/lower_feather_releasefish.xlsx
+++ b/data-raw/lower_feather_releasefish.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="lower_feather_releasefish"/>
   </sheets>
   <definedNames>
-    <definedName name="lower_feather_releasefish">'lower_feather_releasefish'!$A$1:$D$19</definedName>
+    <definedName name="lower_feather_releasefish">'lower_feather_releasefish'!$A$1:$D$20</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -566,6 +566,17 @@
         <v>287</v>
       </c>
     </row>
+    <row outlineLevel="0" r="20">
+      <c r="A20" s="0">
+        <v>12</v>
+      </c>
+      <c r="B20" s="0">
+        <v>19</v>
+      </c>
+      <c r="C20" s="0">
+        <v>288</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
